--- a/data/raw/OM.xlsx
+++ b/data/raw/OM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBA620C0-5682-46FD-B7ED-5FEF14FA4F29}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4F57C6-9873-43E7-B75C-FEC835345E63}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$8:$ZB$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$8:$AL$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1080,12 +1080,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1261,6 +1263,13 @@
     <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1268,17 +1277,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1338,6 +1340,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1627,6 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AL72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1664,292 +1671,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="23"/>
+      <c r="AJ1" s="23"/>
+      <c r="AK1" s="23"/>
+      <c r="AL1" s="23"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="23"/>
-      <c r="AC3" s="23"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
-      <c r="AG3" s="23"/>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="21"/>
+      <c r="AK3" s="21"/>
+      <c r="AL3" s="21"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="23"/>
-      <c r="AG4" s="23"/>
-      <c r="AH4" s="23"/>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="23"/>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="21"/>
+      <c r="AG4" s="21"/>
+      <c r="AH4" s="21"/>
+      <c r="AI4" s="21"/>
+      <c r="AJ4" s="21"/>
+      <c r="AK4" s="21"/>
+      <c r="AL4" s="21"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="23"/>
-      <c r="AH5" s="23"/>
-      <c r="AI5" s="23"/>
-      <c r="AJ5" s="23"/>
-      <c r="AK5" s="23"/>
-      <c r="AL5" s="23"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
+      <c r="AH5" s="21"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="21"/>
+      <c r="AK5" s="21"/>
+      <c r="AL5" s="21"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="23"/>
-      <c r="AJ6" s="23"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21"/>
+      <c r="AC6" s="21"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="21"/>
+      <c r="AH6" s="21"/>
+      <c r="AI6" s="21"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="21"/>
+      <c r="AL6" s="21"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="23"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="23"/>
-      <c r="AI7" s="23"/>
-      <c r="AJ7" s="23"/>
-      <c r="AK7" s="23"/>
-      <c r="AL7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="21"/>
+      <c r="AI7" s="21"/>
+      <c r="AJ7" s="21"/>
+      <c r="AK7" s="21"/>
+      <c r="AL7" s="21"/>
     </row>
     <row r="8" spans="1:38" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -2067,7 +2074,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>392</v>
       </c>
@@ -2165,7 +2172,7 @@
       <c r="AK9" s="9"/>
       <c r="AL9" s="9"/>
     </row>
-    <row r="10" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>394</v>
       </c>
@@ -2267,7 +2274,7 @@
       </c>
       <c r="AL10" s="9"/>
     </row>
-    <row r="11" spans="1:38" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>395</v>
       </c>
@@ -2367,7 +2374,7 @@
       <c r="AK11" s="9"/>
       <c r="AL11" s="9"/>
     </row>
-    <row r="12" spans="1:38" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>396</v>
       </c>
@@ -2471,7 +2478,7 @@
       </c>
       <c r="AL12" s="9"/>
     </row>
-    <row r="13" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>397</v>
       </c>
@@ -2571,7 +2578,7 @@
       </c>
       <c r="AL13" s="9"/>
     </row>
-    <row r="14" spans="1:38" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>398</v>
       </c>
@@ -2671,7 +2678,7 @@
       </c>
       <c r="AL14" s="9"/>
     </row>
-    <row r="15" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>399</v>
       </c>
@@ -2771,7 +2778,7 @@
       </c>
       <c r="AL15" s="9"/>
     </row>
-    <row r="16" spans="1:38" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>400</v>
       </c>
@@ -2871,7 +2878,7 @@
       </c>
       <c r="AL16" s="9"/>
     </row>
-    <row r="17" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>401</v>
       </c>
@@ -2973,7 +2980,7 @@
       </c>
       <c r="AL17" s="9"/>
     </row>
-    <row r="18" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>402</v>
       </c>
@@ -3075,7 +3082,7 @@
       </c>
       <c r="AL18" s="9"/>
     </row>
-    <row r="19" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>403</v>
       </c>
@@ -3177,7 +3184,7 @@
       </c>
       <c r="AL19" s="9"/>
     </row>
-    <row r="20" spans="1:38" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>404</v>
       </c>
@@ -3277,7 +3284,7 @@
       </c>
       <c r="AL20" s="9"/>
     </row>
-    <row r="21" spans="1:38" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>405</v>
       </c>
@@ -3377,7 +3384,7 @@
       </c>
       <c r="AL21" s="9"/>
     </row>
-    <row r="22" spans="1:38" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>406</v>
       </c>
@@ -3477,7 +3484,7 @@
       </c>
       <c r="AL22" s="9"/>
     </row>
-    <row r="23" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>407</v>
       </c>
@@ -3577,7 +3584,7 @@
       <c r="AK23" s="9"/>
       <c r="AL23" s="9"/>
     </row>
-    <row r="24" spans="1:38" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>408</v>
       </c>
@@ -3679,7 +3686,7 @@
       </c>
       <c r="AL24" s="9"/>
     </row>
-    <row r="25" spans="1:38" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>409</v>
       </c>
@@ -3767,7 +3774,7 @@
       <c r="AK25" s="9"/>
       <c r="AL25" s="9"/>
     </row>
-    <row r="26" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>410</v>
       </c>
@@ -3871,7 +3878,7 @@
       </c>
       <c r="AL26" s="9"/>
     </row>
-    <row r="27" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>411</v>
       </c>
@@ -3971,7 +3978,7 @@
       <c r="AK27" s="9"/>
       <c r="AL27" s="9"/>
     </row>
-    <row r="28" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>412</v>
       </c>
@@ -4059,7 +4066,7 @@
       <c r="AK28" s="9"/>
       <c r="AL28" s="9"/>
     </row>
-    <row r="29" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>413</v>
       </c>
@@ -4159,7 +4166,7 @@
       <c r="AK29" s="9"/>
       <c r="AL29" s="9"/>
     </row>
-    <row r="30" spans="1:38" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>414</v>
       </c>
@@ -4253,7 +4260,7 @@
       <c r="AK30" s="9"/>
       <c r="AL30" s="9"/>
     </row>
-    <row r="31" spans="1:38" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>415</v>
       </c>
@@ -4357,7 +4364,7 @@
       <c r="AK31" s="9"/>
       <c r="AL31" s="9"/>
     </row>
-    <row r="32" spans="1:38" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" ht="388.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>416</v>
       </c>
@@ -4457,7 +4464,7 @@
       <c r="AK32" s="9"/>
       <c r="AL32" s="9"/>
     </row>
-    <row r="33" spans="1:38" ht="72" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>417</v>
       </c>
@@ -4555,7 +4562,7 @@
       <c r="AK33" s="9"/>
       <c r="AL33" s="9"/>
     </row>
-    <row r="34" spans="1:38" ht="72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>418</v>
       </c>
@@ -4643,7 +4650,7 @@
       <c r="AK34" s="9"/>
       <c r="AL34" s="9"/>
     </row>
-    <row r="35" spans="1:38" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>419</v>
       </c>
@@ -4733,7 +4740,7 @@
       <c r="AK35" s="9"/>
       <c r="AL35" s="9"/>
     </row>
-    <row r="36" spans="1:38" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>420</v>
       </c>
@@ -4823,7 +4830,7 @@
       <c r="AK36" s="9"/>
       <c r="AL36" s="9"/>
     </row>
-    <row r="37" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>422</v>
       </c>
@@ -4927,7 +4934,7 @@
       </c>
       <c r="AL37" s="9"/>
     </row>
-    <row r="38" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>423</v>
       </c>
@@ -5027,7 +5034,7 @@
       <c r="AK38" s="9"/>
       <c r="AL38" s="9"/>
     </row>
-    <row r="39" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>424</v>
       </c>
@@ -5115,7 +5122,7 @@
       <c r="AK39" s="9"/>
       <c r="AL39" s="9"/>
     </row>
-    <row r="40" spans="1:38" ht="144" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>425</v>
       </c>
@@ -5213,7 +5220,7 @@
       <c r="AK40" s="9"/>
       <c r="AL40" s="9"/>
     </row>
-    <row r="41" spans="1:38" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>426</v>
       </c>
@@ -5307,7 +5314,7 @@
       <c r="AK41" s="9"/>
       <c r="AL41" s="9"/>
     </row>
-    <row r="42" spans="1:38" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>427</v>
       </c>
@@ -5399,7 +5406,7 @@
       <c r="AK42" s="9"/>
       <c r="AL42" s="9"/>
     </row>
-    <row r="43" spans="1:38" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>428</v>
       </c>
@@ -5503,7 +5510,7 @@
       <c r="AK43" s="9"/>
       <c r="AL43" s="9"/>
     </row>
-    <row r="44" spans="1:38" ht="360" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" ht="360" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>429</v>
       </c>
@@ -5595,7 +5602,7 @@
       <c r="AK44" s="9"/>
       <c r="AL44" s="9"/>
     </row>
-    <row r="45" spans="1:38" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>430</v>
       </c>
@@ -5699,7 +5706,7 @@
       <c r="AK45" s="9"/>
       <c r="AL45" s="9"/>
     </row>
-    <row r="46" spans="1:38" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" ht="273.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>431</v>
       </c>
@@ -5797,7 +5804,7 @@
       <c r="AK46" s="9"/>
       <c r="AL46" s="9"/>
     </row>
-    <row r="47" spans="1:38" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>433</v>
       </c>
@@ -5889,7 +5896,7 @@
       <c r="AK47" s="9"/>
       <c r="AL47" s="9"/>
     </row>
-    <row r="48" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>434</v>
       </c>
@@ -5989,7 +5996,7 @@
       <c r="AK48" s="9"/>
       <c r="AL48" s="9"/>
     </row>
-    <row r="49" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>435</v>
       </c>
@@ -6089,7 +6096,7 @@
       <c r="AK49" s="9"/>
       <c r="AL49" s="9"/>
     </row>
-    <row r="50" spans="1:38" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>437</v>
       </c>
@@ -6183,7 +6190,7 @@
       <c r="AK50" s="9"/>
       <c r="AL50" s="9"/>
     </row>
-    <row r="51" spans="1:38" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:38" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>439</v>
       </c>
@@ -6275,7 +6282,7 @@
       <c r="AK51" s="9"/>
       <c r="AL51" s="9"/>
     </row>
-    <row r="52" spans="1:38" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" ht="273.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>440</v>
       </c>
@@ -6375,7 +6382,7 @@
       <c r="AK52" s="9"/>
       <c r="AL52" s="9"/>
     </row>
-    <row r="53" spans="1:38" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>441</v>
       </c>
@@ -6465,7 +6472,7 @@
       <c r="AK53" s="9"/>
       <c r="AL53" s="9"/>
     </row>
-    <row r="54" spans="1:38" ht="288" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:38" ht="288" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>442</v>
       </c>
@@ -6551,7 +6558,7 @@
       <c r="AK54" s="9"/>
       <c r="AL54" s="9"/>
     </row>
-    <row r="55" spans="1:38" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>443</v>
       </c>
@@ -6639,7 +6646,7 @@
       <c r="AK55" s="9"/>
       <c r="AL55" s="9"/>
     </row>
-    <row r="56" spans="1:38" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:38" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>445</v>
       </c>
@@ -6731,7 +6738,7 @@
       <c r="AK56" s="9"/>
       <c r="AL56" s="9"/>
     </row>
-    <row r="57" spans="1:38" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" ht="259.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>446</v>
       </c>
@@ -6821,7 +6828,7 @@
       <c r="AK57" s="9"/>
       <c r="AL57" s="9"/>
     </row>
-    <row r="58" spans="1:38" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:38" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>448</v>
       </c>
@@ -6915,7 +6922,7 @@
       <c r="AK58" s="9"/>
       <c r="AL58" s="9"/>
     </row>
-    <row r="59" spans="1:38" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>449</v>
       </c>
@@ -7009,7 +7016,7 @@
       <c r="AK59" s="9"/>
       <c r="AL59" s="9"/>
     </row>
-    <row r="60" spans="1:38" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>450</v>
       </c>
@@ -7103,7 +7110,7 @@
       <c r="AK60" s="9"/>
       <c r="AL60" s="9"/>
     </row>
-    <row r="61" spans="1:38" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>451</v>
       </c>
@@ -7195,7 +7202,7 @@
       <c r="AK61" s="9"/>
       <c r="AL61" s="9"/>
     </row>
-    <row r="62" spans="1:38" ht="144" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:38" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>452</v>
       </c>
@@ -7289,7 +7296,7 @@
       <c r="AK62" s="9"/>
       <c r="AL62" s="9"/>
     </row>
-    <row r="63" spans="1:38" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:38" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>453</v>
       </c>
@@ -7383,7 +7390,7 @@
       <c r="AK63" s="9"/>
       <c r="AL63" s="9"/>
     </row>
-    <row r="64" spans="1:38" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:38" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>454</v>
       </c>
@@ -7475,7 +7482,7 @@
       <c r="AK64" s="9"/>
       <c r="AL64" s="9"/>
     </row>
-    <row r="65" spans="1:38" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:38" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>455</v>
       </c>
@@ -7567,7 +7574,7 @@
       <c r="AK65" s="9"/>
       <c r="AL65" s="9"/>
     </row>
-    <row r="66" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>456</v>
       </c>
@@ -7655,7 +7662,7 @@
       <c r="AK66" s="9"/>
       <c r="AL66" s="9"/>
     </row>
-    <row r="67" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>457</v>
       </c>
@@ -7743,7 +7750,7 @@
       <c r="AK67" s="9"/>
       <c r="AL67" s="9"/>
     </row>
-    <row r="68" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>458</v>
       </c>
@@ -7831,7 +7838,7 @@
       <c r="AK68" s="9"/>
       <c r="AL68" s="9"/>
     </row>
-    <row r="69" spans="1:38" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:38" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>459</v>
       </c>
@@ -7919,7 +7926,7 @@
       <c r="AK69" s="9"/>
       <c r="AL69" s="9"/>
     </row>
-    <row r="70" spans="1:38" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:38" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>460</v>
       </c>
@@ -8187,7 +8194,18 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A8:ZB8" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A8:AL72" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="1 - Gestión de la Responsabilidad Social_x000a_"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Indicadores"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="8">
     <mergeCell ref="A6:AL6"/>
     <mergeCell ref="A7:AL7"/>
